--- a/04/gdfgfd.xlsx
+++ b/04/gdfgfd.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9075"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -386,12 +386,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -412,7 +412,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -421,15 +421,15 @@
         <v>3</v>
       </c>
       <c r="D2" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -438,72 +438,76 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="E3" s="1">
+        <v>4</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1">
         <v>3</v>
       </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
+      <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
       <c r="D5" s="1">
         <v>3</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
+      <c r="D6" s="1"/>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
   </sheetData>

--- a/04/gdfgfd.xlsx
+++ b/04/gdfgfd.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prepod\PycharmProjects\OGE-2025-2026\04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\OGE-2025-2026\04\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -418,13 +418,15 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1">
         <v>5</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
       <c r="G2" s="1">
         <v>15</v>
       </c>
@@ -434,13 +436,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1">
+      <c r="D3" s="1">
         <v>4</v>
       </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
@@ -449,14 +451,18 @@
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>4</v>
+      </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -464,11 +470,9 @@
         <v>3</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
+      <c r="C5" s="1"/>
       <c r="D5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1">
@@ -482,15 +486,19 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1">
+        <v>4</v>
+      </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -506,7 +514,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1"/>
     </row>

--- a/04/gdfgfd.xlsx
+++ b/04/gdfgfd.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\OGE-2025-2026\04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prepod\PycharmProjects\OGE-2025-2026\04\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -418,14 +418,14 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
         <v>15</v>
@@ -436,13 +436,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="1">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1">
+        <v>6</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
@@ -451,17 +451,15 @@
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1">
         <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -470,14 +468,14 @@
         <v>3</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1">
+        <v>6</v>
+      </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="1">
         <v>6</v>
       </c>
@@ -487,18 +485,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1">
-        <v>2</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -514,7 +510,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1"/>
     </row>
